--- a/Items and Followers.xlsx
+++ b/Items and Followers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Anwender\David\Programmieren\Quest-Game\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F38518D2-07F1-4D4E-B98E-34025289CB12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFC0C8A9-AFA8-4873-B015-321FEC4E2629}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="229">
   <si>
     <t>ATK</t>
   </si>
@@ -459,9 +459,6 @@
     <t>Iron Bracelet</t>
   </si>
   <si>
-    <t>Ring of Defence</t>
-  </si>
-  <si>
     <t>Topas Pendant</t>
   </si>
   <si>
@@ -709,13 +706,19 @@
   </si>
   <si>
     <t>Damage + 10</t>
+  </si>
+  <si>
+    <t>Iron, Force, Fire, Ice</t>
+  </si>
+  <si>
+    <t>Ring of Defense</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -790,6 +793,77 @@
       <name val="Cambria"/>
       <family val="1"/>
     </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FFFFC000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF92D050"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF0070C0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF002060"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color rgb="FF7030A0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -837,7 +911,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -854,6 +928,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1188,16 +1274,16 @@
       <c r="J2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="23" t="s">
         <v>7</v>
       </c>
       <c r="Q2" s="2" t="s">
@@ -1269,43 +1355,43 @@
       </c>
     </row>
     <row r="3" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="15">
         <v>20</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="4" t="s">
+      <c r="H3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="15">
         <v>1</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="M3" s="1">
+      <c r="M3" s="15">
         <v>10</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="N3" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="O3" s="1">
+      <c r="O3" s="15">
         <v>0</v>
       </c>
       <c r="Q3" s="4" t="s">
@@ -1329,79 +1415,79 @@
       <c r="W3" s="1">
         <v>1</v>
       </c>
-      <c r="Y3" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="Z3" s="1">
+      <c r="Y3" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="Z3" s="15">
         <v>10</v>
       </c>
-      <c r="AA3" s="4" t="s">
+      <c r="AA3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AB3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AB3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC3" s="15" t="s">
         <v>27</v>
       </c>
       <c r="AD3" s="13"/>
-      <c r="AE3" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="AF3" s="1">
+      <c r="AE3" s="15" t="s">
+        <v>170</v>
+      </c>
+      <c r="AF3" s="15">
         <v>10</v>
       </c>
-      <c r="AG3" s="4" t="s">
+      <c r="AG3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AH3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ3" s="1" t="s">
+      <c r="AH3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI3" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ3" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="AL3" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="AM3" s="1">
+      <c r="AL3" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="AM3" s="15">
         <v>10</v>
       </c>
-      <c r="AN3" s="4" t="s">
+      <c r="AN3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AO3" s="1" t="s">
+      <c r="AO3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="15">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="4" t="s">
+      <c r="E4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="15">
         <v>2</v>
       </c>
       <c r="Q4" s="4" t="s">
@@ -1425,331 +1511,367 @@
       <c r="W4" s="1">
         <v>2</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Y4" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="Z4" s="1">
+      <c r="Z4" s="15">
         <v>10</v>
       </c>
-      <c r="AA4" s="4" t="s">
+      <c r="AA4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AB4" s="1" t="s">
+      <c r="AB4" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AC4" s="1" t="s">
+      <c r="AC4" s="15" t="s">
         <v>141</v>
       </c>
       <c r="AD4" s="13"/>
-      <c r="AE4" s="1" t="s">
+      <c r="AE4" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="AF4" s="1">
+      <c r="AF4" s="15">
         <v>15</v>
       </c>
-      <c r="AG4" s="4" t="s">
+      <c r="AG4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AH4" s="1" t="s">
+      <c r="AH4" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AI4" s="1" t="s">
+      <c r="AI4" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AJ4" s="1" t="s">
+      <c r="AJ4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="AL4" s="1" t="s">
+      <c r="AL4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="AM4" s="1">
+      <c r="AM4" s="15">
         <v>10</v>
       </c>
-      <c r="AN4" s="4" t="s">
+      <c r="AN4" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AO4" s="1" t="s">
+      <c r="AO4" s="15" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="5" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="15">
         <v>12</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I5" s="4" t="s">
+      <c r="E5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="15">
         <v>2</v>
       </c>
       <c r="Q5" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="R5" s="1"/>
-      <c r="S5" s="1"/>
-      <c r="T5" s="1"/>
-      <c r="U5" s="1"/>
-      <c r="V5" s="1"/>
-      <c r="W5" s="1"/>
-      <c r="Y5" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="Z5" s="1">
+      <c r="R5" s="1">
+        <v>32</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="U5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="W5" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y5" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="Z5" s="15">
         <v>15</v>
       </c>
-      <c r="AA5" s="4" t="s">
+      <c r="AA5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AB5" s="1" t="s">
+      <c r="AB5" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AC5" s="1" t="s">
+      <c r="AC5" s="15" t="s">
         <v>27</v>
       </c>
       <c r="AD5" s="13"/>
-      <c r="AE5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="AF5" s="1">
+      <c r="AE5" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="AF5" s="15">
         <v>20</v>
       </c>
-      <c r="AG5" s="4" t="s">
+      <c r="AG5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AH5" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="AI5" s="1" t="s">
+      <c r="AH5" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="AI5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AJ5" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL5" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="AM5" s="1">
+      <c r="AJ5" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL5" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="AM5" s="15">
         <v>15</v>
       </c>
-      <c r="AN5" s="4" t="s">
+      <c r="AN5" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AO5" s="1" t="s">
+      <c r="AO5" s="15" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="6" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="15">
         <v>15</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="1" t="s">
+      <c r="F6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="15">
         <v>1</v>
       </c>
       <c r="Q6" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="R6" s="1"/>
-      <c r="S6" s="1"/>
-      <c r="T6" s="1"/>
-      <c r="U6" s="1"/>
-      <c r="V6" s="1"/>
-      <c r="W6" s="1"/>
-      <c r="Y6" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z6" s="1">
+      <c r="R6" s="1">
+        <v>30</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W6" s="1">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="Z6" s="15">
         <v>25</v>
       </c>
-      <c r="AA6" s="4" t="s">
+      <c r="AA6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AB6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC6" s="1" t="s">
+      <c r="AB6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC6" s="15" t="s">
         <v>141</v>
       </c>
       <c r="AD6" s="13"/>
-      <c r="AE6" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="AF6" s="1">
+      <c r="AE6" s="15" t="s">
+        <v>173</v>
+      </c>
+      <c r="AF6" s="15">
         <v>25</v>
       </c>
-      <c r="AG6" s="4" t="s">
+      <c r="AG6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AH6" s="1" t="s">
+      <c r="AH6" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="AI6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL6" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="AM6" s="1">
+      <c r="AI6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ6" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL6" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="AM6" s="15">
         <v>20</v>
       </c>
-      <c r="AN6" s="4" t="s">
+      <c r="AN6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AO6" s="1" t="s">
+      <c r="AO6" s="15" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="15">
         <v>12</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="15">
         <v>3</v>
       </c>
       <c r="Q7" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="U7" s="1"/>
-      <c r="V7" s="1"/>
-      <c r="W7" s="1"/>
-      <c r="Y7" s="1" t="s">
+      <c r="R7" s="1">
+        <v>15</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W7" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y7" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z7" s="15">
+        <v>25</v>
+      </c>
+      <c r="AA7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB7" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC7" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="Z7" s="1">
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="AF7" s="15">
+        <v>30</v>
+      </c>
+      <c r="AG7" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="AH7" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="AI7" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ7" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL7" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="AM7" s="15">
         <v>25</v>
       </c>
-      <c r="AA7" s="4" t="s">
+      <c r="AN7" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="AB7" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="AD7" s="13"/>
-      <c r="AE7" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="AF7" s="1">
-        <v>30</v>
-      </c>
-      <c r="AG7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AH7" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI7" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AJ7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL7" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="AM7" s="1">
+      <c r="AO7" s="15" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B8" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="15">
+        <v>10</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AN7" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AO7" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="8" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="1">
-        <v>10</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J8" s="1">
+      <c r="J8" s="15">
         <v>5</v>
       </c>
       <c r="Q8" s="4" t="s">
@@ -1773,163 +1895,175 @@
       <c r="W8" s="1">
         <v>2</v>
       </c>
-      <c r="Y8" s="1" t="s">
-        <v>217</v>
-      </c>
-      <c r="Z8" s="1">
+      <c r="Y8" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="Z8" s="15">
         <v>45</v>
       </c>
-      <c r="AA8" s="5" t="s">
+      <c r="AA8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AB8" s="1" t="s">
+      <c r="AB8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AC8" s="1" t="s">
+      <c r="AC8" s="15" t="s">
         <v>141</v>
       </c>
       <c r="AD8" s="13"/>
-      <c r="AE8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="AF8" s="1">
+      <c r="AE8" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="AF8" s="15">
         <v>45</v>
       </c>
-      <c r="AG8" s="5" t="s">
+      <c r="AG8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AH8" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AI8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL8" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM8" s="1">
+      <c r="AI8" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ8" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL8" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM8" s="15">
         <v>30</v>
       </c>
-      <c r="AN8" s="5" t="s">
+      <c r="AN8" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AO8" s="1" t="s">
-        <v>158</v>
+      <c r="AO8" s="15" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="9" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="17" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="15">
         <v>10</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="15">
         <v>5</v>
       </c>
       <c r="Q9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
-      <c r="V9" s="1"/>
-      <c r="W9" s="1"/>
-      <c r="Y9" s="1" t="s">
-        <v>218</v>
-      </c>
-      <c r="Z9" s="1">
+      <c r="R9" s="1">
         <v>30</v>
       </c>
-      <c r="AA9" s="5" t="s">
+      <c r="S9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W9" s="1">
+        <v>2</v>
+      </c>
+      <c r="Y9" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="Z9" s="15">
+        <v>30</v>
+      </c>
+      <c r="AA9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AB9" s="1" t="s">
+      <c r="AB9" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="AC9" s="1" t="s">
+      <c r="AC9" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="15" t="s">
+        <v>179</v>
+      </c>
+      <c r="AF9" s="15">
+        <v>40</v>
+      </c>
+      <c r="AG9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH9" s="15" t="s">
+        <v>188</v>
+      </c>
+      <c r="AI9" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AJ9" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="AL9" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="AM9" s="15">
+        <v>30</v>
+      </c>
+      <c r="AN9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="AO9" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="AF9" s="1">
+    </row>
+    <row r="10" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B10" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="15">
+        <v>16</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="15" t="s">
         <v>40</v>
       </c>
-      <c r="AG9" s="5" t="s">
+      <c r="H10" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AH9" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="AI9" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AJ9" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="AL9" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="AM9" s="1">
-        <v>30</v>
-      </c>
-      <c r="AN9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="AO9" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="10" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="J10" s="15">
         <v>4</v>
       </c>
       <c r="Q10" s="5" t="s">
@@ -1953,79 +2087,79 @@
       <c r="W10" s="1">
         <v>1</v>
       </c>
-      <c r="Y10" s="1" t="s">
-        <v>216</v>
-      </c>
-      <c r="Z10" s="1">
+      <c r="Y10" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z10" s="15">
         <v>50</v>
       </c>
-      <c r="AA10" s="5" t="s">
+      <c r="AA10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AB10" s="1" t="s">
+      <c r="AB10" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="AC10" s="1" t="s">
-        <v>158</v>
+      <c r="AC10" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="AD10" s="13"/>
-      <c r="AE10" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="AF10" s="1">
+      <c r="AE10" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="AF10" s="15">
         <v>35</v>
       </c>
-      <c r="AG10" s="5" t="s">
+      <c r="AG10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AH10" s="1" t="s">
+      <c r="AH10" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="AI10" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="AI10" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="AJ10" s="1" t="s">
+      <c r="AJ10" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="AL10" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="AM10" s="1">
+      <c r="AL10" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="AM10" s="15">
         <v>30</v>
       </c>
-      <c r="AN10" s="5" t="s">
+      <c r="AN10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AO10" s="1" t="s">
-        <v>160</v>
+      <c r="AO10" s="15" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="15">
         <v>10</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11" s="1" t="s">
+      <c r="E11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="H11" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="15">
         <v>7</v>
       </c>
       <c r="Q11" s="5" t="s">
@@ -2049,79 +2183,79 @@
       <c r="W11" s="1">
         <v>3</v>
       </c>
-      <c r="Y11" s="1" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z11" s="1">
+      <c r="Y11" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="Z11" s="15">
         <v>45</v>
       </c>
-      <c r="AA11" s="5" t="s">
+      <c r="AA11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AB11" s="1" t="s">
+      <c r="AB11" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="AC11" s="1" t="s">
+      <c r="AC11" s="15" t="s">
         <v>27</v>
       </c>
       <c r="AD11" s="13"/>
-      <c r="AE11" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="AF11" s="1">
+      <c r="AE11" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="AF11" s="15">
         <v>30</v>
       </c>
-      <c r="AG11" s="5" t="s">
+      <c r="AG11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AH11" s="1" t="s">
+      <c r="AH11" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="AI11" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="AI11" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AJ11" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL11" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="AM11" s="1">
+      <c r="AJ11" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL11" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="AM11" s="15">
         <v>30</v>
       </c>
-      <c r="AN11" s="5" t="s">
+      <c r="AN11" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AO11" s="1" t="s">
-        <v>161</v>
+      <c r="AO11" s="15" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="15">
         <v>10</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="1" t="s">
+      <c r="E12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="15">
         <v>6</v>
       </c>
       <c r="Q12" s="5" t="s">
@@ -2145,247 +2279,271 @@
       <c r="W12" s="1">
         <v>5</v>
       </c>
-      <c r="Y12" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="Z12" s="1">
+      <c r="Y12" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="Z12" s="15">
         <v>75</v>
       </c>
-      <c r="AA12" s="5" t="s">
+      <c r="AA12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AB12" s="1" t="s">
+      <c r="AB12" s="15" t="s">
         <v>101</v>
       </c>
-      <c r="AC12" s="1" t="s">
-        <v>158</v>
+      <c r="AC12" s="15" t="s">
+        <v>157</v>
       </c>
       <c r="AD12" s="13"/>
-      <c r="AE12" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="AF12" s="1">
+      <c r="AE12" s="15" t="s">
+        <v>176</v>
+      </c>
+      <c r="AF12" s="15">
         <v>45</v>
       </c>
-      <c r="AG12" s="5" t="s">
+      <c r="AG12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AH12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI12" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ12" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL12" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="AM12" s="1">
+      <c r="AH12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI12" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ12" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL12" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="AM12" s="15">
         <v>40</v>
       </c>
-      <c r="AN12" s="5" t="s">
+      <c r="AN12" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="AO12" s="1" t="s">
-        <v>162</v>
+      <c r="AO12" s="15" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="15">
         <v>18</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I13" s="5" t="s">
+      <c r="H13" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="15">
         <v>3</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-      <c r="V13" s="1"/>
-      <c r="W13" s="1"/>
-      <c r="Y13" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="Z13" s="1">
+      <c r="R13" s="1">
+        <v>30</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W13" s="1">
+        <v>3</v>
+      </c>
+      <c r="Y13" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="Z13" s="15">
         <v>100</v>
       </c>
-      <c r="AA13" s="6" t="s">
+      <c r="AA13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AB13" s="1" t="s">
+      <c r="AB13" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="AC13" s="1" t="s">
-        <v>222</v>
+      <c r="AC13" s="15" t="s">
+        <v>221</v>
       </c>
       <c r="AD13" s="13"/>
-      <c r="AE13" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="AF13" s="1">
+      <c r="AE13" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF13" s="15">
         <v>100</v>
       </c>
-      <c r="AG13" s="6" t="s">
+      <c r="AG13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AH13" s="1" t="s">
+      <c r="AH13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AI13" s="1" t="s">
+      <c r="AI13" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="AJ13" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL13" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="AM13" s="1">
+      <c r="AJ13" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL13" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="AM13" s="15">
         <v>75</v>
       </c>
-      <c r="AN13" s="6" t="s">
+      <c r="AN13" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AO13" s="1" t="s">
-        <v>163</v>
+      <c r="AO13" s="15" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="15">
         <v>12</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="1" t="s">
+      <c r="E14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F14" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="15">
         <v>4</v>
       </c>
       <c r="Q14" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="R14" s="1"/>
-      <c r="S14" s="1"/>
-      <c r="T14" s="1"/>
-      <c r="U14" s="1"/>
-      <c r="V14" s="1"/>
-      <c r="W14" s="1"/>
-      <c r="Y14" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z14" s="1">
+      <c r="R14" s="1">
+        <v>20</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="T14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U14" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="V14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W14" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y14" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="Z14" s="15">
         <v>85</v>
       </c>
-      <c r="AA14" s="6" t="s">
+      <c r="AA14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AB14" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="AC14" s="1" t="s">
-        <v>223</v>
+      <c r="AB14" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="AC14" s="15" t="s">
+        <v>222</v>
       </c>
       <c r="AD14" s="13"/>
-      <c r="AE14" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="AF14" s="1">
+      <c r="AE14" s="15" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF14" s="15">
         <v>100</v>
       </c>
-      <c r="AG14" s="6" t="s">
+      <c r="AG14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AH14" s="1" t="s">
+      <c r="AH14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="AI14" s="1" t="s">
+      <c r="AI14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AJ14" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="AL14" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="AM14" s="1">
+      <c r="AJ14" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="AL14" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="AM14" s="15">
         <v>100</v>
       </c>
-      <c r="AN14" s="6" t="s">
+      <c r="AN14" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AO14" s="1" t="s">
-        <v>198</v>
+      <c r="AO14" s="15" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="15" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="15">
         <v>16</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="I15" s="5" t="s">
+      <c r="H15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="15">
         <v>4</v>
       </c>
       <c r="Q15" s="6" t="s">
@@ -2409,79 +2567,79 @@
       <c r="W15" s="1">
         <v>5</v>
       </c>
-      <c r="Y15" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="Z15" s="1">
+      <c r="Y15" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z15" s="15">
         <v>110</v>
       </c>
-      <c r="AA15" s="6" t="s">
+      <c r="AA15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AB15" s="1" t="s">
+      <c r="AB15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="AC15" s="1" t="s">
-        <v>224</v>
+      <c r="AC15" s="15" t="s">
+        <v>223</v>
       </c>
       <c r="AD15" s="13"/>
-      <c r="AE15" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="AF15" s="1">
+      <c r="AE15" s="15" t="s">
+        <v>182</v>
+      </c>
+      <c r="AF15" s="15">
         <v>110</v>
       </c>
-      <c r="AG15" s="6" t="s">
+      <c r="AG15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AH15" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="AI15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL15" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="AM15" s="1">
+      <c r="AH15" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="AI15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL15" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="AM15" s="15">
         <v>100</v>
       </c>
-      <c r="AN15" s="6" t="s">
+      <c r="AN15" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AO15" s="1" t="s">
-        <v>167</v>
+      <c r="AO15" s="15" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="15">
         <v>10</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="7" t="s">
+      <c r="I16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J16" s="1">
+      <c r="J16" s="15">
         <v>7</v>
       </c>
       <c r="Q16" s="6" t="s">
@@ -2505,79 +2663,79 @@
       <c r="W16" s="1">
         <v>4</v>
       </c>
-      <c r="Y16" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="Z16" s="1">
+      <c r="Y16" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="Z16" s="15">
         <v>90</v>
       </c>
-      <c r="AA16" s="6" t="s">
+      <c r="AA16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AB16" s="1" t="s">
+      <c r="AB16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="AC16" s="1" t="s">
+      <c r="AC16" s="15" t="s">
         <v>27</v>
       </c>
       <c r="AD16" s="13"/>
-      <c r="AE16" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="AF16" s="1">
+      <c r="AE16" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="AF16" s="15">
         <v>200</v>
       </c>
-      <c r="AG16" s="6" t="s">
+      <c r="AG16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AH16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AL16" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="AM16" s="1">
+      <c r="AH16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ16" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AL16" s="15" t="s">
+        <v>165</v>
+      </c>
+      <c r="AM16" s="15">
         <v>100</v>
       </c>
-      <c r="AN16" s="6" t="s">
+      <c r="AN16" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="AO16" s="1" t="s">
-        <v>168</v>
+      <c r="AO16" s="15" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="15">
         <v>10</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="F17" s="15" t="s">
         <v>113</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I17" s="7" t="s">
+      <c r="I17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="15">
         <v>8</v>
       </c>
       <c r="Q17" s="6" t="s">
@@ -2601,51 +2759,51 @@
       <c r="W17" s="1">
         <v>4</v>
       </c>
-      <c r="Y17" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="Z17" s="1">
+      <c r="Y17" s="15" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z17" s="15">
         <v>200</v>
       </c>
-      <c r="AA17" s="7" t="s">
+      <c r="AA17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AB17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AC17" s="1" t="s">
-        <v>225</v>
+      <c r="AB17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC17" s="15" t="s">
+        <v>224</v>
       </c>
       <c r="AD17" s="13"/>
-      <c r="AE17" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="AF17" s="1">
+      <c r="AE17" s="15" t="s">
+        <v>184</v>
+      </c>
+      <c r="AF17" s="15">
         <v>250</v>
       </c>
-      <c r="AG17" s="7" t="s">
+      <c r="AG17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AH17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AI17" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ17" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="AL17" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="AM17" s="1">
+      <c r="AH17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AI17" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ17" s="15" t="s">
+        <v>169</v>
+      </c>
+      <c r="AL17" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="AM17" s="15">
         <v>200</v>
       </c>
-      <c r="AN17" s="7" t="s">
+      <c r="AN17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AO17" s="1" t="s">
-        <v>199</v>
+      <c r="AO17" s="15" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="18" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
@@ -2661,57 +2819,69 @@
       <c r="Q18" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="U18" s="1"/>
-      <c r="V18" s="1"/>
-      <c r="W18" s="1"/>
-      <c r="Y18" s="1" t="s">
-        <v>208</v>
-      </c>
-      <c r="Z18" s="1">
+      <c r="R18" s="1">
+        <v>25</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="W18" s="1">
+        <v>7</v>
+      </c>
+      <c r="Y18" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="Z18" s="15">
         <v>250</v>
       </c>
-      <c r="AA18" s="7" t="s">
+      <c r="AA18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AB18" s="1" t="s">
+      <c r="AB18" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="AC18" s="1" t="s">
-        <v>199</v>
+      <c r="AC18" s="15" t="s">
+        <v>198</v>
       </c>
       <c r="AD18" s="13"/>
-      <c r="AE18" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="AF18" s="1">
+      <c r="AE18" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="AF18" s="15">
         <v>250</v>
       </c>
-      <c r="AG18" s="7" t="s">
+      <c r="AG18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AH18" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="AI18" s="1" t="s">
+      <c r="AH18" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="AI18" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="AJ18" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL18" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="AM18" s="1">
+      <c r="AJ18" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL18" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="AM18" s="15">
         <v>250</v>
       </c>
-      <c r="AN18" s="7" t="s">
+      <c r="AN18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AO18" s="1" t="s">
-        <v>169</v>
+      <c r="AO18" s="15" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
@@ -2763,51 +2933,51 @@
       <c r="W19" s="1">
         <v>6</v>
       </c>
-      <c r="Y19" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="Z19" s="1">
+      <c r="Y19" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z19" s="15">
         <v>250</v>
       </c>
-      <c r="AA19" s="7" t="s">
+      <c r="AA19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AB19" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="AC19" s="1" t="s">
-        <v>226</v>
+      <c r="AB19" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="AC19" s="15" t="s">
+        <v>225</v>
       </c>
       <c r="AD19" s="13"/>
-      <c r="AE19" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="AF19" s="1">
+      <c r="AE19" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="AF19" s="15">
         <v>300</v>
       </c>
-      <c r="AG19" s="7" t="s">
+      <c r="AG19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AH19" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="AI19" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ19" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="AL19" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="AM19" s="1">
+      <c r="AH19" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="AI19" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ19" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="AL19" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="AM19" s="15">
         <v>200</v>
       </c>
-      <c r="AN19" s="7" t="s">
+      <c r="AN19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="AO19" s="1" t="s">
-        <v>170</v>
+      <c r="AO19" s="15" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
@@ -2845,51 +3015,51 @@
       <c r="U20" s="1"/>
       <c r="V20" s="1"/>
       <c r="W20" s="1"/>
-      <c r="Y20" s="1" t="s">
-        <v>206</v>
-      </c>
-      <c r="Z20" s="1">
+      <c r="Y20" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="Z20" s="15">
         <v>1000</v>
       </c>
-      <c r="AA20" s="8" t="s">
+      <c r="AA20" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="AB20" s="1" t="s">
-        <v>221</v>
-      </c>
-      <c r="AC20" s="1" t="s">
-        <v>227</v>
+      <c r="AB20" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="AC20" s="15" t="s">
+        <v>226</v>
       </c>
       <c r="AD20" s="13"/>
-      <c r="AE20" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="AF20" s="1">
+      <c r="AE20" s="15" t="s">
+        <v>174</v>
+      </c>
+      <c r="AF20" s="15">
         <v>1000</v>
       </c>
-      <c r="AG20" s="8" t="s">
+      <c r="AG20" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="AH20" s="1" t="s">
+      <c r="AH20" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="AI20" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="AJ20" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="AL20" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="AM20" s="1">
+      <c r="AI20" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ20" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL20" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="AM20" s="15">
         <v>1000</v>
       </c>
-      <c r="AN20" s="8" t="s">
+      <c r="AN20" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="AO20" s="1" t="s">
-        <v>200</v>
+      <c r="AO20" s="15" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="21" spans="2:41" ht="15.75" x14ac:dyDescent="0.25">
